--- a/artfynd/A 57253-2023 artfynd.xlsx
+++ b/artfynd/A 57253-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737551</v>
       </c>
       <c r="B2" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740593</v>
       </c>
       <c r="B3" t="n">
-        <v>106204</v>
+        <v>106207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131740355</v>
       </c>
       <c r="B4" t="n">
-        <v>101203</v>
+        <v>101206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57253-2023 artfynd.xlsx
+++ b/artfynd/A 57253-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131737551</v>
+        <v>131734367</v>
       </c>
       <c r="B2" t="n">
-        <v>96318</v>
+        <v>96037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576407</v>
+        <v>576481</v>
       </c>
       <c r="R2" t="n">
-        <v>6896233</v>
+        <v>6896246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131740593</v>
+        <v>131734368</v>
       </c>
       <c r="B3" t="n">
-        <v>106207</v>
+        <v>96037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576421</v>
+        <v>576253</v>
       </c>
       <c r="R3" t="n">
-        <v>6896235</v>
+        <v>6896186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131740355</v>
+        <v>131734369</v>
       </c>
       <c r="B4" t="n">
-        <v>101206</v>
+        <v>96037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576428</v>
+        <v>576246</v>
       </c>
       <c r="R4" t="n">
-        <v>6896223</v>
+        <v>6896175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,6 +971,1122 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131737551</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96413</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576407</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6896233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131734475</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96410</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lantela Nordost, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576490</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6896244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131733492</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576294</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6896208</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131734452</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99533</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lantela Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576527</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6896306</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131734556</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lantela Väst, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576525</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6896321</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131740016</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576306</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896212</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Allmän i beståndet</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131740593</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>576421</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6896235</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131733134</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>576331</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6896200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131733135</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lantela Nordost, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>576467</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6896231</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131740355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lantela Nord, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>576428</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6896223</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131737244</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lantela Nordost, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>576445</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6896220</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 57253-2023 artfynd.xlsx
+++ b/artfynd/A 57253-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734368</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734369</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734475</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734452</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733134</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733135</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740355</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,8 +2161,29 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737244</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>